--- a/entregables/gestion-proyectos/Mapa_de_usuario_y_validacion_Rehavid.xlsx
+++ b/entregables/gestion-proyectos/Mapa_de_usuario_y_validacion_Rehavid.xlsx
@@ -603,7 +603,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>REHAVID S.A.S. · Rehavid · Gestión de proyectos v7 · Mapa de usuario y guía de validación</t>
+          <t>REHAVID S.A.S. · Rehavid · Gestión de proyectos v8 · Mapa de usuario y guía de validación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2362,7 +2362,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>REHAVID S.A.S. · Rehavid · Gestión de proyectos v7 · Mapa de usuario y guía de validación · Rol: CEO</t>
+          <t>REHAVID S.A.S. · Rehavid · Gestión de proyectos v8 · Mapa de usuario y guía de validación · Rol: CEO</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3045,7 +3045,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>REHAVID S.A.S. · Rehavid · Gestión de proyectos v7 · Mapa de usuario y guía de validación · Rol: Gerente</t>
+          <t>REHAVID S.A.S. · Rehavid · Gestión de proyectos v8 · Mapa de usuario y guía de validación · Rol: Gerente</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3728,7 +3728,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>REHAVID S.A.S. · Rehavid · Gestión de proyectos v7 · Mapa de usuario y guía de validación · Rol: Director de Proyectos</t>
+          <t>REHAVID S.A.S. · Rehavid · Gestión de proyectos v8 · Mapa de usuario y guía de validación · Rol: Director de Proyectos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4469,7 +4469,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>REHAVID S.A.S. · Rehavid · Gestión de proyectos v7 · Mapa de usuario y guía de validación · Rol: Jefe de Operaciones</t>
+          <t>REHAVID S.A.S. · Rehavid · Gestión de proyectos v8 · Mapa de usuario y guía de validación · Rol: Jefe de Operaciones</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5152,7 +5152,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>REHAVID S.A.S. · Rehavid · Gestión de proyectos v7 · Mapa de usuario y guía de validación · Rol: Gestor de Datos</t>
+          <t>REHAVID S.A.S. · Rehavid · Gestión de proyectos v8 · Mapa de usuario y guía de validación · Rol: Gestor de Datos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5777,7 +5777,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>REHAVID S.A.S. · Rehavid · Gestión de proyectos v7 · Mapa de usuario y guía de validación · Rol: Diseñador Ergónomo</t>
+          <t>REHAVID S.A.S. · Rehavid · Gestión de proyectos v8 · Mapa de usuario y guía de validación · Rol: Diseñador Ergónomo</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6402,7 +6402,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>REHAVID S.A.S. · Rehavid · Gestión de proyectos v7 · Mapa de usuario y guía de validación · Rol: Supervisor de Proyectos Especiales</t>
+          <t>REHAVID S.A.S. · Rehavid · Gestión de proyectos v8 · Mapa de usuario y guía de validación · Rol: Supervisor de Proyectos Especiales</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7026,7 +7026,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>REHAVID S.A.S. · Rehavid · Gestión de proyectos v7 · Mapa de usuario y guía de validación</t>
+          <t>REHAVID S.A.S. · Rehavid · Gestión de proyectos v8 · Mapa de usuario y guía de validación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
